--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/8.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/8.xlsx
@@ -426,13 +426,13 @@
         <v>-6.267066176887471</v>
       </c>
       <c r="E2">
-        <v>-4.655332226754829</v>
+        <v>-5.75718240840515</v>
       </c>
       <c r="F2">
-        <v>-6.562330854062205</v>
+        <v>-5.998678195236115</v>
       </c>
       <c r="G2">
-        <v>-10.94910414506704</v>
+        <v>-12.82244585991997</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.479170849407777</v>
       </c>
       <c r="E3">
-        <v>-4.791440041529369</v>
+        <v>-6.545644074828651</v>
       </c>
       <c r="F3">
-        <v>-6.305034140180859</v>
+        <v>-5.932413773216571</v>
       </c>
       <c r="G3">
-        <v>-10.70228311184114</v>
+        <v>-12.56997703600407</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.879020246145849</v>
       </c>
       <c r="E4">
-        <v>-6.888168791820822</v>
+        <v>-5.907681713576067</v>
       </c>
       <c r="F4">
-        <v>-6.652036416846169</v>
+        <v>-5.545673055504164</v>
       </c>
       <c r="G4">
-        <v>-10.76524968799808</v>
+        <v>-12.74103954510929</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.23505222548865</v>
       </c>
       <c r="E5">
-        <v>-6.452891870203547</v>
+        <v>-7.385195985006689</v>
       </c>
       <c r="F5">
-        <v>-6.091036190443844</v>
+        <v>-5.438384566228377</v>
       </c>
       <c r="G5">
-        <v>-10.72304685346345</v>
+        <v>-12.24033277447668</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.50553323531472</v>
       </c>
       <c r="E6">
-        <v>-8.20686042285443</v>
+        <v>-8.608323229056429</v>
       </c>
       <c r="F6">
-        <v>-6.845187258340632</v>
+        <v>-5.422508904953725</v>
       </c>
       <c r="G6">
-        <v>-11.00943883752026</v>
+        <v>-12.45901417061878</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.58308011338296</v>
       </c>
       <c r="E7">
-        <v>-7.637921062426757</v>
+        <v>-9.281100498479985</v>
       </c>
       <c r="F7">
-        <v>-6.197464834355523</v>
+        <v>-5.38192221568616</v>
       </c>
       <c r="G7">
-        <v>-10.0224791380795</v>
+        <v>-12.15398050463033</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.39790589627442</v>
       </c>
       <c r="E8">
-        <v>-8.89887012138856</v>
+        <v>-9.646136259764283</v>
       </c>
       <c r="F8">
-        <v>-5.977816590564013</v>
+        <v>-5.451764356518395</v>
       </c>
       <c r="G8">
-        <v>-11.03208959009995</v>
+        <v>-12.42757723017786</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.8610653162901</v>
       </c>
       <c r="E9">
-        <v>-8.702773611434411</v>
+        <v>-10.33582285113248</v>
       </c>
       <c r="F9">
-        <v>-5.471926819102535</v>
+        <v>-4.959710805785877</v>
       </c>
       <c r="G9">
-        <v>-10.55336815239364</v>
+        <v>-12.93379936967889</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.91372933035614</v>
       </c>
       <c r="E10">
-        <v>-10.63206203529225</v>
+        <v>-10.28864973739458</v>
       </c>
       <c r="F10">
-        <v>-5.284562538100329</v>
+        <v>-5.051292620737183</v>
       </c>
       <c r="G10">
-        <v>-10.16211132783488</v>
+        <v>-12.16449810780859</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.51294457725337</v>
       </c>
       <c r="E11">
-        <v>-11.62526959702455</v>
+        <v>-12.0604151928956</v>
       </c>
       <c r="F11">
-        <v>-5.56715427899356</v>
+        <v>-4.558712228336484</v>
       </c>
       <c r="G11">
-        <v>-10.10812957227152</v>
+        <v>-11.97457211022061</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.65503565921983</v>
       </c>
       <c r="E12">
-        <v>-10.74430932052038</v>
+        <v>-12.144481784374</v>
       </c>
       <c r="F12">
-        <v>-5.489570216414761</v>
+        <v>-4.493727633954266</v>
       </c>
       <c r="G12">
-        <v>-9.028908279196809</v>
+        <v>-11.45964654649683</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.3677440184167</v>
       </c>
       <c r="E13">
-        <v>-12.73401664458856</v>
+        <v>-12.63477060823645</v>
       </c>
       <c r="F13">
-        <v>-5.490604847300858</v>
+        <v>-4.384006229616458</v>
       </c>
       <c r="G13">
-        <v>-9.097962948600468</v>
+        <v>-11.22046625237556</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.719263738838897</v>
       </c>
       <c r="E14">
-        <v>-12.8354725762564</v>
+        <v>-13.86919186646132</v>
       </c>
       <c r="F14">
-        <v>-5.105906883603754</v>
+        <v>-3.98038172750019</v>
       </c>
       <c r="G14">
-        <v>-8.822717571374383</v>
+        <v>-10.65729610850798</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.804883287111235</v>
       </c>
       <c r="E15">
-        <v>-12.83653676764821</v>
+        <v>-13.42236733612449</v>
       </c>
       <c r="F15">
-        <v>-4.973851037351665</v>
+        <v>-4.201311455663832</v>
       </c>
       <c r="G15">
-        <v>-9.602006749136663</v>
+        <v>-10.51635625326459</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.734909417579846</v>
       </c>
       <c r="E16">
-        <v>-13.99480267848608</v>
+        <v>-14.74796036154579</v>
       </c>
       <c r="F16">
-        <v>-4.555021851557012</v>
+        <v>-3.958075450077605</v>
       </c>
       <c r="G16">
-        <v>-8.2378567331335</v>
+        <v>-10.331816513269</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.628500999469153</v>
       </c>
       <c r="E17">
-        <v>-14.04707938243063</v>
+        <v>-15.45932928646271</v>
       </c>
       <c r="F17">
-        <v>-4.505410099435947</v>
+        <v>-3.533537984510261</v>
       </c>
       <c r="G17">
-        <v>-7.837098642877026</v>
+        <v>-9.513661530875671</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.606257768812513</v>
       </c>
       <c r="E18">
-        <v>-14.95954878108017</v>
+        <v>-16.25044011018069</v>
       </c>
       <c r="F18">
-        <v>-3.971104840956238</v>
+        <v>-3.273854744141449</v>
       </c>
       <c r="G18">
-        <v>-7.839859637856778</v>
+        <v>-9.410902197336695</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.2247027362417904</v>
       </c>
       <c r="E19">
-        <v>-16.47442296307408</v>
+        <v>-17.40994682289667</v>
       </c>
       <c r="F19">
-        <v>-3.861894539305957</v>
+        <v>-2.786487267806569</v>
       </c>
       <c r="G19">
-        <v>-6.77883972415698</v>
+        <v>-9.325135894050796</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.781467877400343</v>
       </c>
       <c r="E20">
-        <v>-17.93899485579078</v>
+        <v>-17.86777554507215</v>
       </c>
       <c r="F20">
-        <v>-3.557451294694277</v>
+        <v>-3.103199462021112</v>
       </c>
       <c r="G20">
-        <v>-7.243862124421786</v>
+        <v>-9.64721886956649</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.999015158864677</v>
       </c>
       <c r="E21">
-        <v>-17.37793051166244</v>
+        <v>-19.43206896391176</v>
       </c>
       <c r="F21">
-        <v>-3.762216261359689</v>
+        <v>-2.51791895867533</v>
       </c>
       <c r="G21">
-        <v>-6.698022686452292</v>
+        <v>-9.463758367416698</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.843179703904522</v>
       </c>
       <c r="E22">
-        <v>-18.21676692294727</v>
+        <v>-19.30426184199328</v>
       </c>
       <c r="F22">
-        <v>-3.511697249568049</v>
+        <v>-2.552927421852443</v>
       </c>
       <c r="G22">
-        <v>-7.257004990212693</v>
+        <v>-8.582828820507714</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.314751014869882</v>
       </c>
       <c r="E23">
-        <v>-18.33512311961174</v>
+        <v>-20.05447148847399</v>
       </c>
       <c r="F23">
-        <v>-3.385995809662835</v>
+        <v>-2.394432573205202</v>
       </c>
       <c r="G23">
-        <v>-7.313102184375643</v>
+        <v>-8.137384986562157</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.429784464407669</v>
       </c>
       <c r="E24">
-        <v>-18.81733767431852</v>
+        <v>-20.04195025784278</v>
       </c>
       <c r="F24">
-        <v>-2.704359610023415</v>
+        <v>-2.182085559701965</v>
       </c>
       <c r="G24">
-        <v>-7.426329462909796</v>
+        <v>-8.469436014696598</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.225157051126346</v>
       </c>
       <c r="E25">
-        <v>-19.29084850198256</v>
+        <v>-20.33629201139334</v>
       </c>
       <c r="F25">
-        <v>-2.918936588574987</v>
+        <v>-2.545252597865505</v>
       </c>
       <c r="G25">
-        <v>-7.202420715361189</v>
+        <v>-9.193538398319227</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.753930427224508</v>
       </c>
       <c r="E26">
-        <v>-20.46754983050566</v>
+        <v>-20.09815314875198</v>
       </c>
       <c r="F26">
-        <v>-2.660270583376814</v>
+        <v>-2.119825465707555</v>
       </c>
       <c r="G26">
-        <v>-7.096556090106375</v>
+        <v>-8.409743568077998</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.073113176947246</v>
       </c>
       <c r="E27">
-        <v>-20.13573042606762</v>
+        <v>-20.65931711930848</v>
       </c>
       <c r="F27">
-        <v>-2.515313743193525</v>
+        <v>-2.009083512729497</v>
       </c>
       <c r="G27">
-        <v>-8.300280379821997</v>
+        <v>-8.657372374415484</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.238678041902716</v>
       </c>
       <c r="E28">
-        <v>-20.56996127018913</v>
+        <v>-20.69583926218034</v>
       </c>
       <c r="F28">
-        <v>-2.241534174731275</v>
+        <v>-2.425389491415222</v>
       </c>
       <c r="G28">
-        <v>-8.600056899494081</v>
+        <v>-8.59461105208198</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.307725307148363</v>
       </c>
       <c r="E29">
-        <v>-19.83389857650838</v>
+        <v>-20.27502175806956</v>
       </c>
       <c r="F29">
-        <v>-2.244761494132582</v>
+        <v>-2.2766942291431</v>
       </c>
       <c r="G29">
-        <v>-7.657875639017501</v>
+        <v>-8.589039403939386</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.333065158817024</v>
       </c>
       <c r="E30">
-        <v>-18.61646815276029</v>
+        <v>-20.64576339660352</v>
       </c>
       <c r="F30">
-        <v>-2.949386545934494</v>
+        <v>-2.255275961576316</v>
       </c>
       <c r="G30">
-        <v>-7.817940515841263</v>
+        <v>-9.727294345070382</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.6415515930393484</v>
       </c>
       <c r="E31">
-        <v>-18.81120612051214</v>
+        <v>-20.59609056521338</v>
       </c>
       <c r="F31">
-        <v>-2.590608198270986</v>
+        <v>-2.396414856400101</v>
       </c>
       <c r="G31">
-        <v>-7.961929383526324</v>
+        <v>-8.981931637994553</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.57540815472893</v>
       </c>
       <c r="E32">
-        <v>-18.54738628177328</v>
+        <v>-19.95046602593982</v>
       </c>
       <c r="F32">
-        <v>-2.821404610569374</v>
+        <v>-2.423050181869717</v>
       </c>
       <c r="G32">
-        <v>-8.692788590594606</v>
+        <v>-9.274133629472784</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.433758630254186</v>
       </c>
       <c r="E33">
-        <v>-18.09265956429306</v>
+        <v>-19.82551184264617</v>
       </c>
       <c r="F33">
-        <v>-2.99864044333755</v>
+        <v>-2.120453368198877</v>
       </c>
       <c r="G33">
-        <v>-8.200811728549054</v>
+        <v>-9.211236574772171</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.186157546944244</v>
       </c>
       <c r="E34">
-        <v>-17.26409826053164</v>
+        <v>-19.228527642689</v>
       </c>
       <c r="F34">
-        <v>-2.846289595716873</v>
+        <v>-1.976853393821374</v>
       </c>
       <c r="G34">
-        <v>-8.129360224174965</v>
+        <v>-8.470710574729216</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.806950667712865</v>
       </c>
       <c r="E35">
-        <v>-18.47855800533069</v>
+        <v>-18.80928604753288</v>
       </c>
       <c r="F35">
-        <v>-2.688286797306896</v>
+        <v>-2.263316095587888</v>
       </c>
       <c r="G35">
-        <v>-8.058699940184761</v>
+        <v>-8.915128139557599</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.27771555044129</v>
       </c>
       <c r="E36">
-        <v>-16.64220292505826</v>
+        <v>-17.74017673295802</v>
       </c>
       <c r="F36">
-        <v>-2.641586756606671</v>
+        <v>-2.466894011765089</v>
       </c>
       <c r="G36">
-        <v>-7.844613581251171</v>
+        <v>-8.608757013171285</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.587464613731369</v>
       </c>
       <c r="E37">
-        <v>-17.1212611333817</v>
+        <v>-18.2297727002973</v>
       </c>
       <c r="F37">
-        <v>-3.418895249432421</v>
+        <v>-2.290887476222666</v>
       </c>
       <c r="G37">
-        <v>-7.504315984178407</v>
+        <v>-8.293288507643055</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.732296817642353</v>
       </c>
       <c r="E38">
-        <v>-16.07529232098603</v>
+        <v>-17.74219643236544</v>
       </c>
       <c r="F38">
-        <v>-2.580429219625386</v>
+        <v>-1.969118099014032</v>
       </c>
       <c r="G38">
-        <v>-7.427100820020446</v>
+        <v>-8.1840736103025</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.717554894005328</v>
       </c>
       <c r="E39">
-        <v>-15.61372760775423</v>
+        <v>-17.51614859532456</v>
       </c>
       <c r="F39">
-        <v>-2.669739651158215</v>
+        <v>-2.493196333538779</v>
       </c>
       <c r="G39">
-        <v>-7.972950189626558</v>
+        <v>-7.998802239742727</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.557357817404876</v>
       </c>
       <c r="E40">
-        <v>-16.24717055194716</v>
+        <v>-17.27560964145913</v>
       </c>
       <c r="F40">
-        <v>-2.980051878818729</v>
+        <v>-2.344590534946159</v>
       </c>
       <c r="G40">
-        <v>-7.047255445935549</v>
+        <v>-7.526149032009901</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.272789202448708</v>
       </c>
       <c r="E41">
-        <v>-14.8012786145121</v>
+        <v>-16.65518153156425</v>
       </c>
       <c r="F41">
-        <v>-2.428735267355129</v>
+        <v>-2.431804368582501</v>
       </c>
       <c r="G41">
-        <v>-6.370447515886947</v>
+        <v>-7.453535526151526</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.890971518693087</v>
       </c>
       <c r="E42">
-        <v>-14.4191252214788</v>
+        <v>-16.09831055436702</v>
       </c>
       <c r="F42">
-        <v>-3.117487142984598</v>
+        <v>-2.356336784717855</v>
       </c>
       <c r="G42">
-        <v>-6.695543087843378</v>
+        <v>-7.907573536317031</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.441956510281382</v>
       </c>
       <c r="E43">
-        <v>-13.85260859464523</v>
+        <v>-15.76616509980043</v>
       </c>
       <c r="F43">
-        <v>-2.724581715060556</v>
+        <v>-2.453792552922412</v>
       </c>
       <c r="G43">
-        <v>-6.267122079060754</v>
+        <v>-7.598130223670275</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.959673271716285</v>
       </c>
       <c r="E44">
-        <v>-13.39957099796987</v>
+        <v>-14.9740308409567</v>
       </c>
       <c r="F44">
-        <v>-2.979381729589865</v>
+        <v>-2.370975693460128</v>
       </c>
       <c r="G44">
-        <v>-5.719312866495394</v>
+        <v>-7.537957747948481</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.482865279557092</v>
       </c>
       <c r="E45">
-        <v>-12.74424646737188</v>
+        <v>-14.8687619341744</v>
       </c>
       <c r="F45">
-        <v>-3.726541790790726</v>
+        <v>-2.481542032548792</v>
       </c>
       <c r="G45">
-        <v>-6.657643962509801</v>
+        <v>-7.199169759641625</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.051984248719906</v>
       </c>
       <c r="E46">
-        <v>-12.407794434024</v>
+        <v>-14.50380315694823</v>
       </c>
       <c r="F46">
-        <v>-3.183876648481964</v>
+        <v>-2.422821552466544</v>
       </c>
       <c r="G46">
-        <v>-5.713489616891816</v>
+        <v>-7.429865125545738</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.706836383131932</v>
       </c>
       <c r="E47">
-        <v>-12.73134937339804</v>
+        <v>-14.22255322175385</v>
       </c>
       <c r="F47">
-        <v>-3.483879015447236</v>
+        <v>-2.788270742824796</v>
       </c>
       <c r="G47">
-        <v>-6.571854485405128</v>
+        <v>-7.48608812043918</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.490146857114582</v>
       </c>
       <c r="E48">
-        <v>-11.13442829933316</v>
+        <v>-12.86960368485221</v>
       </c>
       <c r="F48">
-        <v>-3.356550661962924</v>
+        <v>-2.972568407701838</v>
       </c>
       <c r="G48">
-        <v>-6.898234549030795</v>
+        <v>-7.298777453827216</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.434580765043942</v>
       </c>
       <c r="E49">
-        <v>-9.783358079144712</v>
+        <v>-12.927337199976</v>
       </c>
       <c r="F49">
-        <v>-3.605185137913196</v>
+        <v>-2.924269617914211</v>
       </c>
       <c r="G49">
-        <v>-5.925867734327141</v>
+        <v>-6.940748574846116</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.556502057086566</v>
       </c>
       <c r="E50">
-        <v>-10.98110775485547</v>
+        <v>-12.15235227219933</v>
       </c>
       <c r="F50">
-        <v>-3.705713320814735</v>
+        <v>-2.875857341792399</v>
       </c>
       <c r="G50">
-        <v>-6.279927269206655</v>
+        <v>-6.628809110862749</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.863588147598318</v>
       </c>
       <c r="E51">
-        <v>-11.09071946821113</v>
+        <v>-11.79709348629759</v>
       </c>
       <c r="F51">
-        <v>-3.899297812644563</v>
+        <v>-3.186896876032571</v>
       </c>
       <c r="G51">
-        <v>-5.923043838982142</v>
+        <v>-7.279394209694783</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.343083521103994</v>
       </c>
       <c r="E52">
-        <v>-10.29159777397357</v>
+        <v>-11.24499552070444</v>
       </c>
       <c r="F52">
-        <v>-3.959903656935583</v>
+        <v>-3.050809365631058</v>
       </c>
       <c r="G52">
-        <v>-5.251820799258292</v>
+        <v>-7.209154364988067</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.962188157203994</v>
       </c>
       <c r="E53">
-        <v>-9.818508094392248</v>
+        <v>-10.80340137784647</v>
       </c>
       <c r="F53">
-        <v>-3.675417439792149</v>
+        <v>-2.899231384797193</v>
       </c>
       <c r="G53">
-        <v>-5.556602863785754</v>
+        <v>-7.270932455296406</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.676076957982155</v>
       </c>
       <c r="E54">
-        <v>-10.38824446624527</v>
+        <v>-11.74197742915023</v>
       </c>
       <c r="F54">
-        <v>-3.90654354231685</v>
+        <v>-2.896408308688452</v>
       </c>
       <c r="G54">
-        <v>-5.802341348620315</v>
+        <v>-7.816394491074424</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.432001185582835</v>
       </c>
       <c r="E55">
-        <v>-8.468868871990221</v>
+        <v>-10.5937149173953</v>
       </c>
       <c r="F55">
-        <v>-4.212478676620972</v>
+        <v>-3.212226694475375</v>
       </c>
       <c r="G55">
-        <v>-6.116353214111266</v>
+        <v>-7.61286877241111</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.172171883519248</v>
       </c>
       <c r="E56">
-        <v>-8.830703002151099</v>
+        <v>-10.49317826595101</v>
       </c>
       <c r="F56">
-        <v>-4.133034100855485</v>
+        <v>-3.4130304082206</v>
       </c>
       <c r="G56">
-        <v>-6.11501906425894</v>
+        <v>-7.711450197479527</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.842826103909113</v>
       </c>
       <c r="E57">
-        <v>-7.69276993960766</v>
+        <v>-9.56197457033173</v>
       </c>
       <c r="F57">
-        <v>-4.148056543705255</v>
+        <v>-3.337522234353217</v>
       </c>
       <c r="G57">
-        <v>-6.589791021136899</v>
+        <v>-7.32051780638361</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.406618545487358</v>
       </c>
       <c r="E58">
-        <v>-8.24400749513935</v>
+        <v>-10.07320758647966</v>
       </c>
       <c r="F58">
-        <v>-3.885285978026209</v>
+        <v>-3.654395960211306</v>
       </c>
       <c r="G58">
-        <v>-6.256707102794207</v>
+        <v>-7.462934164937518</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.835912031812375</v>
       </c>
       <c r="E59">
-        <v>-6.397490519193708</v>
+        <v>-8.567684703311595</v>
       </c>
       <c r="F59">
-        <v>-3.96397425435294</v>
+        <v>-3.281894049785619</v>
       </c>
       <c r="G59">
-        <v>-6.225859439459278</v>
+        <v>-6.982991135927216</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.115406852577801</v>
       </c>
       <c r="E60">
-        <v>-6.615559185033073</v>
+        <v>-8.870861509651119</v>
       </c>
       <c r="F60">
-        <v>-4.612132813775622</v>
+        <v>-3.509251908994985</v>
       </c>
       <c r="G60">
-        <v>-6.56380654919916</v>
+        <v>-7.339305152318974</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.246283129604726</v>
       </c>
       <c r="E61">
-        <v>-6.240270958595408</v>
+        <v>-8.686190339618321</v>
       </c>
       <c r="F61">
-        <v>-4.283028243215197</v>
+        <v>-3.665150654201852</v>
       </c>
       <c r="G61">
-        <v>-6.573354162534417</v>
+        <v>-7.95717544013193</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.239999230065266</v>
       </c>
       <c r="E62">
-        <v>-5.570554937601039</v>
+        <v>-8.045818830193657</v>
       </c>
       <c r="F62">
-        <v>-4.348765823566561</v>
+        <v>-3.718198474309729</v>
       </c>
       <c r="G62">
-        <v>-6.295125983777449</v>
+        <v>-7.520365508952794</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.114500407414626</v>
       </c>
       <c r="E63">
-        <v>-7.050410430093628</v>
+        <v>-8.708044755179339</v>
       </c>
       <c r="F63">
-        <v>-4.502274728816351</v>
+        <v>-3.591114489209243</v>
       </c>
       <c r="G63">
-        <v>-7.484750660041315</v>
+        <v>-8.118577777353558</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.893056722860959</v>
       </c>
       <c r="E64">
-        <v>-6.569472905057013</v>
+        <v>-7.442155131075167</v>
       </c>
       <c r="F64">
-        <v>-4.656235094300667</v>
+        <v>-3.796178496507066</v>
       </c>
       <c r="G64">
-        <v>-7.468320422529912</v>
+        <v>-7.394667405372206</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.602866513672705</v>
       </c>
       <c r="E65">
-        <v>-5.759215693234593</v>
+        <v>-8.018747612575803</v>
       </c>
       <c r="F65">
-        <v>-4.360393616799658</v>
+        <v>-3.704861759124658</v>
       </c>
       <c r="G65">
-        <v>-6.807055503788188</v>
+        <v>-7.951216458161243</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.26795208086609</v>
       </c>
       <c r="E66">
-        <v>-6.203807685885646</v>
+        <v>-8.236028323937834</v>
       </c>
       <c r="F66">
-        <v>-4.439783520316559</v>
+        <v>-3.725937910954085</v>
       </c>
       <c r="G66">
-        <v>-7.605578951133634</v>
+        <v>-8.031957353318528</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.906744907536074</v>
       </c>
       <c r="E67">
-        <v>-4.095395472654404</v>
+        <v>-8.177638180082933</v>
       </c>
       <c r="F67">
-        <v>-4.623833503340165</v>
+        <v>-3.800464469449151</v>
       </c>
       <c r="G67">
-        <v>-7.423581710112201</v>
+        <v>-8.112244703736932</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.539940374260808</v>
       </c>
       <c r="E68">
-        <v>-5.985453726183797</v>
+        <v>-8.121752282354272</v>
       </c>
       <c r="F68">
-        <v>-4.671544980639208</v>
+        <v>-3.740445937646716</v>
       </c>
       <c r="G68">
-        <v>-6.627994716660089</v>
+        <v>-7.822363404681729</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.181506188152814</v>
       </c>
       <c r="E69">
-        <v>-5.362222490878164</v>
+        <v>-6.822021371990781</v>
       </c>
       <c r="F69">
-        <v>-4.989608242087717</v>
+        <v>-3.96303322898336</v>
       </c>
       <c r="G69">
-        <v>-6.602288330547648</v>
+        <v>-7.613669924431613</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.837038729802358</v>
       </c>
       <c r="E70">
-        <v>-5.831607878721212</v>
+        <v>-7.230992388097499</v>
       </c>
       <c r="F70">
-        <v>-4.582566724434901</v>
+        <v>-3.921316646578377</v>
       </c>
       <c r="G70">
-        <v>-6.38514964862685</v>
+        <v>-7.966070875995952</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.511748104107435</v>
       </c>
       <c r="E71">
-        <v>-6.267912763938228</v>
+        <v>-7.670313237003623</v>
       </c>
       <c r="F71">
-        <v>-5.115778537942916</v>
+        <v>-4.366524363947777</v>
       </c>
       <c r="G71">
-        <v>-6.706908190679695</v>
+        <v>-7.261709275423997</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.208837213912737</v>
       </c>
       <c r="E72">
-        <v>-5.021835213617615</v>
+        <v>-7.364845022816219</v>
       </c>
       <c r="F72">
-        <v>-5.077507135566176</v>
+        <v>-4.130809934378969</v>
       </c>
       <c r="G72">
-        <v>-6.72632785081306</v>
+        <v>-7.421261017689171</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.927300665503959</v>
       </c>
       <c r="E73">
-        <v>-6.073016299596111</v>
+        <v>-8.183819547103402</v>
       </c>
       <c r="F73">
-        <v>-5.173958094111136</v>
+        <v>-4.198538909966662</v>
       </c>
       <c r="G73">
-        <v>-6.324712329261915</v>
+        <v>-7.595988300706366</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.664867087823851</v>
       </c>
       <c r="E74">
-        <v>-6.544077222821997</v>
+        <v>-7.974690088955178</v>
       </c>
       <c r="F74">
-        <v>-4.950442202915954</v>
+        <v>-4.01515576270231</v>
       </c>
       <c r="G74">
-        <v>-6.140689034370448</v>
+        <v>-7.034705167796171</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.423181513623879</v>
       </c>
       <c r="E75">
-        <v>-5.55593702350428</v>
+        <v>-7.772081633377999</v>
       </c>
       <c r="F75">
-        <v>-5.605350299936646</v>
+        <v>-4.45516464625174</v>
       </c>
       <c r="G75">
-        <v>-5.601176048926502</v>
+        <v>-6.848093026292994</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.201745389630707</v>
       </c>
       <c r="E76">
-        <v>-6.228483340753442</v>
+        <v>-8.325094350720695</v>
       </c>
       <c r="F76">
-        <v>-5.779155034922427</v>
+        <v>-4.384330949638355</v>
       </c>
       <c r="G76">
-        <v>-5.937686381902339</v>
+        <v>-6.493235649938516</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.997032156369283</v>
       </c>
       <c r="E77">
-        <v>-7.544743181244931</v>
+        <v>-8.872134010847274</v>
       </c>
       <c r="F77">
-        <v>-5.062678530688661</v>
+        <v>-4.345492115590697</v>
       </c>
       <c r="G77">
-        <v>-6.120342421486088</v>
+        <v>-6.817470480054736</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.811787745323735</v>
       </c>
       <c r="E78">
-        <v>-7.118183572092422</v>
+        <v>-8.962703491000681</v>
       </c>
       <c r="F78">
-        <v>-5.555311938603139</v>
+        <v>-4.713497647753988</v>
       </c>
       <c r="G78">
-        <v>-5.864781548036509</v>
+        <v>-6.695390802748571</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.64609446593805</v>
       </c>
       <c r="E79">
-        <v>-7.81210428665779</v>
+        <v>-9.783779227227425</v>
       </c>
       <c r="F79">
-        <v>-5.725757643770567</v>
+        <v>-5.033671589344831</v>
       </c>
       <c r="G79">
-        <v>-5.637760887680987</v>
+        <v>-6.377389729882799</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.497992211730572</v>
       </c>
       <c r="E80">
-        <v>-9.47232437040188</v>
+        <v>-10.03945234122649</v>
       </c>
       <c r="F80">
-        <v>-5.512701547770535</v>
+        <v>-4.990762157879817</v>
       </c>
       <c r="G80">
-        <v>-4.782425168336109</v>
+        <v>-6.129360347535062</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.367204661891897</v>
       </c>
       <c r="E81">
-        <v>-9.060935149175068</v>
+        <v>-11.12081570646611</v>
       </c>
       <c r="F81">
-        <v>-5.716332479461515</v>
+        <v>-4.838173568814536</v>
       </c>
       <c r="G81">
-        <v>-4.737865225377519</v>
+        <v>-5.887369400250956</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.253359049246035</v>
       </c>
       <c r="E82">
-        <v>-10.76235076096694</v>
+        <v>-12.15160960246207</v>
       </c>
       <c r="F82">
-        <v>-5.798366531728153</v>
+        <v>-4.717694157016571</v>
       </c>
       <c r="G82">
-        <v>-4.403433915000343</v>
+        <v>-5.793200932386387</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.154037056670621</v>
       </c>
       <c r="E83">
-        <v>-12.5053287072012</v>
+        <v>-12.44058511431354</v>
       </c>
       <c r="F83">
-        <v>-5.799431812208153</v>
+        <v>-5.118324939339121</v>
       </c>
       <c r="G83">
-        <v>-5.028964805191174</v>
+        <v>-5.727195275424399</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.065693147446012</v>
       </c>
       <c r="E84">
-        <v>-11.20883565575319</v>
+        <v>-13.24828826679563</v>
       </c>
       <c r="F84">
-        <v>-6.291358622728042</v>
+        <v>-5.26099465712328</v>
       </c>
       <c r="G84">
-        <v>-4.675223082683429</v>
+        <v>-5.387625998370274</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.986850950158193</v>
       </c>
       <c r="E85">
-        <v>-13.3078376999965</v>
+        <v>-13.60289042396626</v>
       </c>
       <c r="F85">
-        <v>-6.19527380257512</v>
+        <v>-5.550906680755051</v>
       </c>
       <c r="G85">
-        <v>-5.018566381652322</v>
+        <v>-5.490961366833085</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.913173657476028</v>
       </c>
       <c r="E86">
-        <v>-14.08393663237906</v>
+        <v>-15.11332670143265</v>
       </c>
       <c r="F86">
-        <v>-6.62540896086688</v>
+        <v>-5.607009519844453</v>
       </c>
       <c r="G86">
-        <v>-5.577545374867183</v>
+        <v>-4.618933876879201</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.837771347252731</v>
       </c>
       <c r="E87">
-        <v>-16.0534877186391</v>
+        <v>-16.69935226703506</v>
       </c>
       <c r="F87">
-        <v>-6.189458663407467</v>
+        <v>-5.620834971797176</v>
       </c>
       <c r="G87">
-        <v>-5.270803467380473</v>
+        <v>-5.316482374731336</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.757756586302286</v>
       </c>
       <c r="E88">
-        <v>-16.512751967075</v>
+        <v>-16.83920060133994</v>
       </c>
       <c r="F88">
-        <v>-6.480829442035567</v>
+        <v>-5.450751263184771</v>
       </c>
       <c r="G88">
-        <v>-4.741265155646349</v>
+        <v>-4.682963138154245</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.672428242774457</v>
       </c>
       <c r="E89">
-        <v>-17.9393616621854</v>
+        <v>-18.50833272193113</v>
       </c>
       <c r="F89">
-        <v>-6.66155270156953</v>
+        <v>-5.980509612990514</v>
       </c>
       <c r="G89">
-        <v>-4.566842442818769</v>
+        <v>-5.122355294854013</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.583631859729797</v>
       </c>
       <c r="E90">
-        <v>-20.0893724376511</v>
+        <v>-20.8079914494543</v>
       </c>
       <c r="F90">
-        <v>-6.3454659247441</v>
+        <v>-5.925026392718405</v>
       </c>
       <c r="G90">
-        <v>-5.01294507532664</v>
+        <v>-5.284274077179767</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.498663373622015</v>
       </c>
       <c r="E91">
-        <v>-21.96546487734084</v>
+        <v>-22.20030248243061</v>
       </c>
       <c r="F91">
-        <v>-6.956365760939964</v>
+        <v>-5.94567262186578</v>
       </c>
       <c r="G91">
-        <v>-3.678215877530979</v>
+        <v>-5.651916780406911</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.430296731531913</v>
       </c>
       <c r="E92">
-        <v>-24.05960786897391</v>
+        <v>-24.23359184034861</v>
       </c>
       <c r="F92">
-        <v>-6.948017888438252</v>
+        <v>-6.079161543724712</v>
       </c>
       <c r="G92">
-        <v>-5.574211655509138</v>
+        <v>-5.712165398676107</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.392498608343114</v>
       </c>
       <c r="E93">
-        <v>-26.02696264534023</v>
+        <v>-25.85715845547461</v>
       </c>
       <c r="F93">
-        <v>-6.716803150601452</v>
+        <v>-6.287316189802381</v>
       </c>
       <c r="G93">
-        <v>-5.767766011008167</v>
+        <v>-5.744062504946985</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.399033950803642</v>
       </c>
       <c r="E94">
-        <v>-28.38494358960819</v>
+        <v>-28.01318757289651</v>
       </c>
       <c r="F94">
-        <v>-7.446874820649962</v>
+        <v>-6.083384560744184</v>
       </c>
       <c r="G94">
-        <v>-5.431441068582529</v>
+        <v>-6.03634394951816</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.465460003587422</v>
       </c>
       <c r="E95">
-        <v>-29.61823725780515</v>
+        <v>-30.22450482947805</v>
       </c>
       <c r="F95">
-        <v>-6.718290484273178</v>
+        <v>-5.980902259139441</v>
       </c>
       <c r="G95">
-        <v>-6.248808141137506</v>
+        <v>-6.292590105894368</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.604855041658913</v>
       </c>
       <c r="E96">
-        <v>-32.32874405391123</v>
+        <v>-32.24168187687676</v>
       </c>
       <c r="F96">
-        <v>-6.637315499731019</v>
+        <v>-6.237236824282435</v>
       </c>
       <c r="G96">
-        <v>-6.611077828954413</v>
+        <v>-7.090815604141279</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.813179994111299</v>
       </c>
       <c r="E97">
-        <v>-34.5033557644236</v>
+        <v>-35.2166062702907</v>
       </c>
       <c r="F97">
-        <v>-7.113124765694638</v>
+        <v>-6.435684246950397</v>
       </c>
       <c r="G97">
-        <v>-7.029454642570887</v>
+        <v>-7.206628418741603</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.094142102106673</v>
       </c>
       <c r="E98">
-        <v>-36.56393823518582</v>
+        <v>-37.35153949154787</v>
       </c>
       <c r="F98">
-        <v>-6.861646504450556</v>
+        <v>-6.411874482691731</v>
       </c>
       <c r="G98">
-        <v>-7.393459056250372</v>
+        <v>-7.899194545557135</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.420444196080501</v>
       </c>
       <c r="E99">
-        <v>-40.27152670253776</v>
+        <v>-39.39846861317697</v>
       </c>
       <c r="F99">
-        <v>-7.558090599782421</v>
+        <v>-6.397456748046006</v>
       </c>
       <c r="G99">
-        <v>-7.571053271704575</v>
+        <v>-8.161644664273938</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.794453334904612</v>
       </c>
       <c r="E100">
-        <v>-42.29036117142328</v>
+        <v>-41.84862438163406</v>
       </c>
       <c r="F100">
-        <v>-6.745177633433245</v>
+        <v>-6.34149183212917</v>
       </c>
       <c r="G100">
-        <v>-8.175390049352991</v>
+        <v>-8.754060167435437</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.160775698408453</v>
       </c>
       <c r="E101">
-        <v>-44.46847792081758</v>
+        <v>-44.25786085895784</v>
       </c>
       <c r="F101">
-        <v>-7.17824935416793</v>
+        <v>-6.228193951529774</v>
       </c>
       <c r="G101">
-        <v>-7.482913307267019</v>
+        <v>-8.345737480621729</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.561421266081719</v>
       </c>
       <c r="E102">
-        <v>-46.36538549128358</v>
+        <v>-46.31821011330867</v>
       </c>
       <c r="F102">
-        <v>-6.887796406622131</v>
+        <v>-6.109781316401794</v>
       </c>
       <c r="G102">
-        <v>-9.096320918012989</v>
+        <v>-9.70817594458109</v>
       </c>
     </row>
   </sheetData>
